--- a/output/pdf_financials_xlsx/AGF.B.xlsx
+++ b/output/pdf_financials_xlsx/AGF.B.xlsx
@@ -967,19 +967,19 @@
         <v>379.47</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>627.389</v>
+        <v>409.881</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>624.909</v>
+        <v>381.745</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>637.22</v>
+        <v>356.804</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>744.933</v>
+        <v>422.884</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>793.011</v>
+        <v>424.927</v>
       </c>
     </row>
     <row r="11">
@@ -1029,19 +1029,19 @@
         </is>
       </c>
       <c r="N11" s="3" t="n">
-        <v>-165.71</v>
+        <v>51.798</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>-155.905</v>
+        <v>87.259</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>-165.396</v>
+        <v>115.02</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>-196.741</v>
+        <v>125.308</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>-204.337</v>
+        <v>163.747</v>
       </c>
     </row>
     <row r="12">
@@ -1051,16 +1051,16 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>302981</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.226204</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.183879</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.171343</v>
       </c>
       <c r="F12" s="1" t="inlineStr">
         <is>
@@ -2069,16 +2069,16 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>141278</v>
+        <v>-161703</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.116271</v>
+        <v>-0.109933</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.16383</v>
+        <v>-0.020049</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.162178</v>
+        <v>-0.009165</v>
       </c>
       <c r="F27" s="1" t="inlineStr">
         <is>
@@ -2189,16 +2189,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>141278</v>
+        <v>-161703</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.116271</v>
+        <v>-0.109933</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.16383</v>
+        <v>-0.020049</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.162178</v>
+        <v>-0.009165</v>
       </c>
       <c r="F29" s="1" t="inlineStr">
         <is>
@@ -2249,16 +2249,16 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>22.47155625046724</v>
+        <v>-25.72033905044879</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>23.73531483163729</v>
+        <v>-22.44148898165821</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>31.01765865239888</v>
+        <v>-3.795843486064489</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>27.12582772595518</v>
+        <v>-1.532934251923067</v>
       </c>
       <c r="F30" s="1" t="inlineStr">
         <is>
@@ -7788,16 +7788,16 @@
         <v>0</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>22</v>
+        <v>17.239</v>
       </c>
       <c r="P124" s="3" t="n">
-        <v>-16</v>
+        <v>-21.647</v>
       </c>
       <c r="Q124" s="3" t="n">
-        <v>9</v>
+        <v>-6.117</v>
       </c>
       <c r="R124" s="3" t="n">
-        <v>0</v>
+        <v>-6.201</v>
       </c>
     </row>
     <row r="125">
@@ -7850,16 +7850,16 @@
         <v>0</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>22</v>
+        <v>17.239</v>
       </c>
       <c r="P125" s="3" t="n">
-        <v>-16</v>
+        <v>-21.647</v>
       </c>
       <c r="Q125" s="3" t="n">
-        <v>9</v>
+        <v>-6.117</v>
       </c>
       <c r="R125" s="3" t="n">
-        <v>0</v>
+        <v>-6.201</v>
       </c>
     </row>
     <row r="126">
@@ -40898,7 +40898,11 @@
           <t>Lease payments 11</t>
         </is>
       </c>
-      <c r="D327" t="inlineStr"/>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E327" t="inlineStr">
         <is>
           <t>-</t>
@@ -43600,7 +43604,11 @@
           <t>Lease payments 10</t>
         </is>
       </c>
-      <c r="D355" t="inlineStr"/>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E355" t="inlineStr">
         <is>
           <t>-</t>
@@ -45647,7 +45655,11 @@
           <t>Lease payments 7</t>
         </is>
       </c>
-      <c r="D376" t="inlineStr"/>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E376" t="inlineStr">
         <is>
           <t>-</t>
@@ -59705,7 +59717,7 @@
       </c>
       <c r="D518" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E518" t="inlineStr">
@@ -59808,7 +59820,7 @@
       </c>
       <c r="D519" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E519" t="inlineStr">
@@ -61667,7 +61679,7 @@
       </c>
       <c r="D538" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E538" t="inlineStr">
@@ -63308,7 +63320,7 @@
       </c>
       <c r="D555" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E555" t="inlineStr">
@@ -64722,7 +64734,7 @@
       </c>
       <c r="D569" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E569" t="inlineStr">
@@ -66322,7 +66334,7 @@
       </c>
       <c r="D585" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E585" t="inlineStr">
@@ -68773,7 +68785,7 @@
       </c>
       <c r="D610" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E610" t="inlineStr">
@@ -68876,7 +68888,7 @@
       </c>
       <c r="D611" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E611" t="inlineStr">
@@ -68933,7 +68945,7 @@
         <v>378.822</v>
       </c>
       <c r="P611" s="5" t="n">
-        <v>-0.648</v>
+        <v>0.648</v>
       </c>
       <c r="Q611" t="inlineStr">
         <is>
@@ -71571,7 +71583,7 @@
       </c>
       <c r="D638" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E638" t="inlineStr">
@@ -72670,7 +72682,7 @@
       </c>
       <c r="D649" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E649" t="inlineStr">
@@ -74620,7 +74632,7 @@
       </c>
       <c r="D669" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E669" t="inlineStr">
@@ -74723,7 +74735,7 @@
       </c>
       <c r="D670" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E670" t="inlineStr">
@@ -74826,7 +74838,7 @@
       </c>
       <c r="D671" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E671" t="inlineStr">
@@ -75626,7 +75638,7 @@
       </c>
       <c r="D679" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E679" s="5" t="n">
@@ -78103,7 +78115,7 @@
       </c>
       <c r="D704" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E704" t="inlineStr">
@@ -78206,7 +78218,7 @@
       </c>
       <c r="D705" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E705" t="inlineStr">
@@ -78309,7 +78321,7 @@
       </c>
       <c r="D706" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E706" s="5" t="n">
@@ -81075,7 +81087,7 @@
       </c>
       <c r="D734" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E734" s="5" t="n">
@@ -81178,7 +81190,7 @@
       </c>
       <c r="D735" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E735" s="5" t="n">

--- a/output/pdf_financials_xlsx/AGF.B.xlsx
+++ b/output/pdf_financials_xlsx/AGF.B.xlsx
@@ -2167,13 +2167,13 @@
         <v>4.24</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>10.49</v>
+        <v>6.38</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>11.652</v>
+        <v>5.447</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>9.119999999999999</v>
+        <v>4.325</v>
       </c>
       <c r="Q28" s="3" t="n">
         <v>0</v>
@@ -2227,13 +2227,13 @@
         <v>61.457</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>62.288</v>
+        <v>58.178</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>98.911</v>
+        <v>92.706</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>124.14</v>
+        <v>119.345</v>
       </c>
       <c r="Q29" s="3" t="n">
         <v>125.308</v>
@@ -2289,13 +2289,13 @@
         </is>
       </c>
       <c r="N30" s="3" t="n">
-        <v>13.49162513348019</v>
+        <v>12.60139620818794</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>21.08958558988836</v>
+        <v>19.76656915506051</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>26.3106582115365</v>
+        <v>25.29438943334803</v>
       </c>
       <c r="Q30" s="3" t="n">
         <v>22.85841457007764</v>
@@ -63219,7 +63219,11 @@
           <t>Depreciation of right-of-use assets 7</t>
         </is>
       </c>
-      <c r="D554" t="inlineStr"/>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E554" t="inlineStr">
         <is>
           <t>-</t>
@@ -64633,7 +64637,11 @@
           <t>Depreciation of right-of-use asset 6</t>
         </is>
       </c>
-      <c r="D568" t="inlineStr"/>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E568" t="inlineStr">
         <is>
           <t>-</t>
